--- a/branches/effective-period-master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/effective-period-master/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$194</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7656" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7250" uniqueCount="816">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T11:48:03+00:00</t>
+    <t>2026-10-09T12:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1565,13 +1565,128 @@
     <t>Untersuchungszeitpunkt</t>
   </si>
   <si>
-    <t>Klinischer Bezugszeitpunkt der Laboruntersuchung</t>
+    <t>Klinischer Bezugszeitpunkt der Laboruntersuchung; ein Zeitraum, wenn die Probe über einen Zeitraum gewonnen wurde, z. B. 24-Stunden-Sammelurin.</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+mii-lab-1:Datetime must be at least to day {($this as dateTime).hasValue() implies ($this as dateTime).toString().length() &gt;= 8}</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.effective[x].id</t>
+  </si>
+  <si>
+    <t>Observation.effective[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.effective[x].extension:QuelleKlinischesBezugsdatum</t>
+  </si>
+  <si>
+    <t>QuelleKlinischesBezugsdatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum}
+</t>
+  </si>
+  <si>
+    <t>Quelle klinisches Bezugsdatum</t>
+  </si>
+  <si>
+    <t>Datum der Probenentnahme | Datum des Eingangs der Probe im Labor</t>
+  </si>
+  <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
+    <t>Dokumentationsdatum</t>
+  </si>
+  <si>
+    <t>Zeitpunkt, an dem das Ergebnis der Laboruntersuchung dokumentiert wurde</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Durchführendes Labor</t>
+  </si>
+  <si>
+    <t>Organisation (Labor), die die Laboruntersuchung durchgeführt hat.</t>
+  </si>
+  <si>
+    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.type</t>
+  </si>
+  <si>
+    <t>Observation.performer.identifier</t>
+  </si>
+  <si>
+    <t>Observation.performer.display</t>
+  </si>
+  <si>
+    <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptRangeRatio</t>
+  </si>
+  <si>
+    <t>Messwert</t>
+  </si>
+  <si>
+    <t>Wert der Analyse</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -1581,237 +1696,6 @@
     <t>closed</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mii-lab-1:Datetime must be at least to day {($this as dateTime).hasValue() implies ($this as dateTime).toString().length() &gt;= 8}</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].id</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].extension:QuelleKlinischesBezugsdatum</t>
-  </si>
-  <si>
-    <t>QuelleKlinischesBezugsdatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum}
-</t>
-  </si>
-  <si>
-    <t>Quelle klinisches Bezugsdatum</t>
-  </si>
-  <si>
-    <t>Datum der Probenentnahme | Datum des Eingangs der Probe im Labor</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime</t>
-  </si>
-  <si>
-    <t>effectiveDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>Klinischer Bezugszeitpunkt der Laboruntersuchung, in der Regel der Zeitpunkt der Probenentnahme.</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime.extension</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime.extension:QuelleKlinischesBezugsdatum</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime.value</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectivePeriod</t>
-  </si>
-  <si>
-    <t>effectivePeriod</t>
-  </si>
-  <si>
-    <t>Untersuchungszeitraum</t>
-  </si>
-  <si>
-    <t>Klinischer Bezugszeitraum der Laboruntersuchung, wenn die Probe über einen Zeitraum gewonnen wurde, z. B. 24-Stunden-Sammelurin.</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectivePeriod.id</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectivePeriod.extension</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectivePeriod.extension:QuelleKlinischesBezugsdatum</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectivePeriod.start</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectivePeriod.end</t>
-  </si>
-  <si>
-    <t>Observation.effective[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t>Dokumentationsdatum</t>
-  </si>
-  <si>
-    <t>Zeitpunkt, an dem das Ergebnis der Laboruntersuchung dokumentiert wurde</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Durchführendes Labor</t>
-  </si>
-  <si>
-    <t>Organisation (Labor), die die Laboruntersuchung durchgeführt hat.</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.reference</t>
-  </si>
-  <si>
-    <t>Observation.performer.type</t>
-  </si>
-  <si>
-    <t>Observation.performer.identifier</t>
-  </si>
-  <si>
-    <t>Observation.performer.display</t>
-  </si>
-  <si>
-    <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-CodeableConceptRangeRatio</t>
-  </si>
-  <si>
-    <t>Messwert</t>
-  </si>
-  <si>
-    <t>Wert der Analyse</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
     <t xml:space="preserve">obs-7
 </t>
   </si>
@@ -1907,6 +1791,12 @@
     <t>Observation.value[x].value.id</t>
   </si>
   <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueQuantity.value.extension</t>
   </si>
   <si>
@@ -1939,6 +1829,9 @@
   </si>
   <si>
     <t>Primitive value for decimal</t>
+  </si>
+  <si>
+    <t>The actual value</t>
   </si>
   <si>
     <t>decimal.value</t>
@@ -2988,7 +2881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO205"/>
+  <dimension ref="A1:AO194"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -15114,7 +15007,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>492</v>
       </c>
@@ -15191,14 +15084,16 @@
         <v>82</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AC104" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>492</v>
@@ -15213,19 +15108,19 @@
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AK104" t="s" s="2">
+      <c r="AN104" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15233,10 +15128,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15348,10 +15243,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15465,13 +15360,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B107" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C107" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>82</v>
@@ -15493,13 +15388,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15582,16 +15477,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15610,20 +15503,18 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>514</v>
+        <v>127</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15671,7 +15562,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15686,27 +15577,27 @@
         <v>104</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15717,19 +15608,19 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>106</v>
+        <v>517</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>518</v>
@@ -15738,7 +15629,9 @@
         <v>519</v>
       </c>
       <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15786,31 +15679,31 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>109</v>
+        <v>516</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15818,10 +15711,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15832,7 +15725,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15844,13 +15737,13 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15889,29 +15782,31 @@
         <v>82</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC110" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15929,28 +15824,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>82</v>
@@ -15959,15 +15852,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>509</v>
+        <v>112</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>510</v>
+        <v>113</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -16004,16 +15899,16 @@
         <v>82</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>119</v>
@@ -16025,7 +15920,7 @@
         <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>120</v>
@@ -16046,12 +15941,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16065,24 +15960,26 @@
         <v>92</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>514</v>
+        <v>106</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>524</v>
+        <v>449</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16131,7 +16028,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>526</v>
+        <v>452</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16140,10 +16037,10 @@
         <v>92</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -16161,18 +16058,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
         <v>527</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16182,7 +16077,7 @@
         <v>92</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>82</v>
@@ -16191,20 +16086,18 @@
         <v>93</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>327</v>
+        <v>133</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>529</v>
+        <v>455</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>530</v>
+        <v>456</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -16228,13 +16121,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16252,7 +16145,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16267,27 +16160,27 @@
         <v>104</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16301,24 +16194,26 @@
         <v>92</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>106</v>
+        <v>203</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16367,7 +16262,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>109</v>
+        <v>465</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16379,7 +16274,7 @@
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>82</v>
@@ -16399,21 +16294,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>82</v>
@@ -16422,19 +16317,19 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>113</v>
+        <v>467</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>114</v>
+        <v>468</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>115</v>
+        <v>469</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16472,31 +16367,31 @@
         <v>82</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>119</v>
+        <v>470</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>82</v>
@@ -16514,16 +16409,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16541,19 +16434,23 @@
         <v>82</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16589,56 +16486,56 @@
         <v>82</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>119</v>
+        <v>530</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16650,7 +16547,7 @@
         <v>92</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>82</v>
@@ -16659,18 +16556,20 @@
         <v>93</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16718,7 +16617,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16727,7 +16626,7 @@
         <v>92</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>104</v>
@@ -16736,24 +16635,24 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM117" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO117" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16773,27 +16672,23 @@
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>514</v>
+        <v>106</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>544</v>
+        <v>107</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q118" t="s" s="2">
-        <v>547</v>
-      </c>
+      <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16837,7 +16732,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>548</v>
+        <v>109</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16846,10 +16741,10 @@
         <v>92</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>540</v>
+        <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>82</v>
@@ -16858,53 +16753,53 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>550</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>551</v>
+        <v>113</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>552</v>
+        <v>114</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>553</v>
+        <v>115</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16942,56 +16837,58 @@
         <v>82</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF119" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C120" s="2"/>
+      <c r="C120" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="D120" t="s" s="2">
         <v>82</v>
       </c>
@@ -17003,27 +16900,27 @@
         <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>82</v>
       </c>
@@ -17071,7 +16968,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>556</v>
+        <v>119</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17083,30 +16980,30 @@
         <v>82</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17114,31 +17011,35 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>106</v>
+        <v>559</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>107</v>
+        <v>560</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17186,7 +17087,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>109</v>
+        <v>564</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17198,7 +17099,7 @@
         <v>82</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>82</v>
@@ -17207,7 +17108,7 @@
         <v>82</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>82</v>
+        <v>565</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>82</v>
@@ -17218,21 +17119,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>82</v>
@@ -17244,17 +17145,15 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>113</v>
+        <v>568</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -17291,31 +17190,31 @@
         <v>82</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>82</v>
@@ -17333,12 +17232,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17349,29 +17248,27 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>449</v>
+        <v>193</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -17408,31 +17305,29 @@
         <v>82</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC123" s="2"/>
       <c r="AD123" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>452</v>
+        <v>119</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>82</v>
@@ -17450,14 +17345,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="D124" t="s" s="2">
         <v>82</v>
       </c>
@@ -17469,25 +17366,25 @@
         <v>92</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>133</v>
+        <v>574</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>455</v>
+        <v>575</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>456</v>
+        <v>576</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>457</v>
+        <v>577</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17513,13 +17410,13 @@
         <v>82</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>82</v>
@@ -17537,19 +17434,19 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>460</v>
+        <v>119</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>82</v>
@@ -17558,7 +17455,7 @@
         <v>82</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>82</v>
@@ -17567,12 +17464,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17586,26 +17483,24 @@
         <v>92</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>203</v>
+        <v>559</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>462</v>
+        <v>580</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17654,7 +17549,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>465</v>
+        <v>582</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17666,7 +17561,7 @@
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>82</v>
@@ -17684,12 +17579,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17703,31 +17598,33 @@
         <v>92</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>467</v>
+        <v>585</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q126" s="2"/>
+      <c r="Q126" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="R126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17747,13 +17644,13 @@
         <v>82</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>82</v>
@@ -17771,7 +17668,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>470</v>
+        <v>591</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17792,7 +17689,7 @@
         <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>82</v>
@@ -17801,12 +17698,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17814,7 +17711,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>92</v>
@@ -17829,19 +17726,17 @@
         <v>93</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>571</v>
+        <v>106</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>574</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>82</v>
@@ -17878,17 +17773,19 @@
         <v>82</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AC127" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>570</v>
+        <v>598</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17897,7 +17794,7 @@
         <v>92</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>104</v>
@@ -17906,34 +17803,32 @@
         <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>581</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>92</v>
@@ -17948,26 +17843,24 @@
         <v>93</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>582</v>
+        <v>133</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>574</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>82</v>
@@ -18009,7 +17902,7 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>570</v>
+        <v>606</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18018,7 +17911,7 @@
         <v>92</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>104</v>
@@ -18027,24 +17920,24 @@
         <v>82</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18052,31 +17945,35 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>107</v>
+        <v>610</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -18124,7 +18021,7 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>109</v>
+        <v>614</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18136,7 +18033,7 @@
         <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>82</v>
@@ -18145,7 +18042,7 @@
         <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>82</v>
@@ -18154,46 +18051,50 @@
         <v>82</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="D130" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>113</v>
+        <v>545</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>114</v>
+        <v>546</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
       </c>
@@ -18217,70 +18118,66 @@
         <v>82</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y130" s="2"/>
       <c r="Z130" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>119</v>
+        <v>530</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
@@ -18289,7 +18186,7 @@
         <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>82</v>
@@ -18301,17 +18198,15 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>591</v>
+        <v>106</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>592</v>
+        <v>107</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18360,19 +18255,19 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>82</v>
@@ -18390,48 +18285,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>596</v>
+        <v>550</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>597</v>
+        <v>112</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>598</v>
+        <v>113</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>599</v>
+        <v>114</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
@@ -18467,31 +18360,31 @@
         <v>82</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>602</v>
+        <v>119</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>82</v>
@@ -18500,7 +18393,7 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>603</v>
+        <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>82</v>
@@ -18509,12 +18402,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18522,31 +18415,35 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>518</v>
+        <v>247</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
       </c>
@@ -18594,19 +18491,19 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>82</v>
@@ -18615,7 +18512,7 @@
         <v>82</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>82</v>
@@ -18626,10 +18523,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18640,7 +18537,7 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18652,13 +18549,13 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18697,29 +18594,31 @@
         <v>82</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC134" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>82</v>
@@ -18737,28 +18636,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>82</v>
@@ -18767,16 +18664,16 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>610</v>
+        <v>112</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>611</v>
+        <v>113</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>612</v>
+        <v>114</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>613</v>
+        <v>115</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18814,16 +18711,16 @@
         <v>82</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF135" t="s" s="2">
         <v>119</v>
@@ -18835,7 +18732,7 @@
         <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>120</v>
@@ -18847,7 +18744,7 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>82</v>
@@ -18856,12 +18753,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136" hidden="true">
+    <row r="136">
       <c r="A136" t="s" s="2">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18869,31 +18766,35 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>597</v>
+        <v>133</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>616</v>
+        <v>262</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
@@ -18941,7 +18842,7 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>617</v>
+        <v>267</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18953,7 +18854,7 @@
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>82</v>
@@ -18962,7 +18863,7 @@
         <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -18973,10 +18874,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18993,30 +18894,28 @@
         <v>93</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J137" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>620</v>
+        <v>271</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q137" t="s" s="2">
-        <v>623</v>
-      </c>
+      <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
         <v>82</v>
       </c>
@@ -19036,13 +18935,13 @@
         <v>82</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>82</v>
@@ -19060,7 +18959,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>626</v>
+        <v>274</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19081,7 +18980,7 @@
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>627</v>
+        <v>275</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
@@ -19092,10 +18991,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19118,17 +19017,17 @@
         <v>93</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>630</v>
+        <v>278</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>631</v>
+        <v>279</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>632</v>
+        <v>280</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19177,7 +19076,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>633</v>
+        <v>282</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19198,7 +19097,7 @@
         <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>634</v>
+        <v>283</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
@@ -19207,12 +19106,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19220,13 +19119,13 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>82</v>
@@ -19235,24 +19134,24 @@
         <v>93</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>637</v>
+        <v>286</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>638</v>
+        <v>287</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>639</v>
+        <v>288</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>640</v>
+        <v>82</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>82</v>
@@ -19294,7 +19193,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>641</v>
+        <v>289</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19303,7 +19202,7 @@
         <v>92</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>642</v>
+        <v>82</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>104</v>
@@ -19315,21 +19214,21 @@
         <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="AN139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>643</v>
-      </c>
       <c r="B140" t="s" s="2">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19337,13 +19236,13 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>82</v>
@@ -19352,19 +19251,19 @@
         <v>93</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>167</v>
+        <v>293</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>645</v>
+        <v>294</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>646</v>
+        <v>295</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>647</v>
+        <v>296</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>648</v>
+        <v>297</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19413,7 +19312,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>649</v>
+        <v>298</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19434,7 +19333,7 @@
         <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>634</v>
+        <v>299</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
@@ -19443,16 +19342,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19464,7 +19361,7 @@
         <v>92</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>82</v>
@@ -19473,19 +19370,19 @@
         <v>93</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>583</v>
+        <v>302</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>584</v>
+        <v>303</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>574</v>
+        <v>304</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>575</v>
+        <v>305</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19510,11 +19407,13 @@
         <v>82</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y141" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z141" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19532,7 +19431,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>570</v>
+        <v>306</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19541,7 +19440,7 @@
         <v>92</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>104</v>
@@ -19550,26 +19449,28 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>578</v>
+        <v>307</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>639</v>
+      </c>
       <c r="D142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19581,25 +19482,29 @@
         <v>92</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>106</v>
+        <v>640</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>107</v>
+        <v>545</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19647,7 +19552,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>109</v>
+        <v>530</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19656,67 +19561,71 @@
         <v>92</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C143" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>642</v>
+      </c>
       <c r="D143" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>112</v>
+        <v>643</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>113</v>
+        <v>545</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>114</v>
+        <v>546</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O143" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19752,54 +19661,54 @@
         <v>82</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC143" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>119</v>
+        <v>530</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19807,10 +19716,10 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>93</v>
@@ -19819,22 +19728,22 @@
         <v>82</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>145</v>
+        <v>232</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>247</v>
+        <v>645</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>248</v>
+        <v>646</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>249</v>
+        <v>647</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>250</v>
+        <v>648</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -19859,13 +19768,13 @@
         <v>82</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y144" t="s" s="2">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>82</v>
@@ -19883,16 +19792,16 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>252</v>
+        <v>644</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>104</v>
@@ -19904,7 +19813,7 @@
         <v>82</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>82</v>
@@ -19913,26 +19822,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>82</v>
@@ -19941,16 +19850,20 @@
         <v>82</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>107</v>
+        <v>654</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
       </c>
@@ -19974,13 +19887,13 @@
         <v>82</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>82</v>
+        <v>659</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>82</v>
@@ -19998,46 +19911,46 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>109</v>
+        <v>652</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
     </row>
-    <row r="146" hidden="true">
+    <row r="146">
       <c r="A146" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20047,7 +19960,7 @@
         <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>82</v>
@@ -20056,18 +19969,20 @@
         <v>82</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>112</v>
+        <v>664</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>113</v>
+        <v>665</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>114</v>
+        <v>666</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
       </c>
@@ -20103,19 +20018,19 @@
         <v>82</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE146" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>119</v>
+        <v>663</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20127,7 +20042,7 @@
         <v>82</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>82</v>
@@ -20136,7 +20051,7 @@
         <v>82</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>82</v>
@@ -20145,12 +20060,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20158,35 +20073,33 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>133</v>
+        <v>232</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>262</v>
+        <v>671</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>263</v>
+        <v>672</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
@@ -20210,13 +20123,13 @@
         <v>82</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>82</v>
+        <v>675</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -20234,7 +20147,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>267</v>
+        <v>670</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20252,24 +20165,24 @@
         <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>268</v>
+        <v>677</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20289,21 +20202,23 @@
         <v>82</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>271</v>
+        <v>680</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>272</v>
+        <v>681</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>682</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>683</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
       </c>
@@ -20327,13 +20242,13 @@
         <v>82</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>82</v>
+        <v>684</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>82</v>
+        <v>685</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20351,7 +20266,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>274</v>
+        <v>679</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20372,7 +20287,7 @@
         <v>82</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>275</v>
+        <v>686</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>82</v>
@@ -20381,12 +20296,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>665</v>
+        <v>687</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20394,33 +20309,31 @@
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>278</v>
+        <v>107</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="N149" s="2"/>
-      <c r="O149" t="s" s="2">
-        <v>280</v>
-      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>82</v>
       </c>
@@ -20468,7 +20381,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>282</v>
+        <v>109</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20480,7 +20393,7 @@
         <v>82</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>82</v>
@@ -20489,7 +20402,7 @@
         <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>82</v>
@@ -20500,21 +20413,21 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>82</v>
@@ -20523,21 +20436,21 @@
         <v>82</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>286</v>
+        <v>113</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>82</v>
       </c>
@@ -20573,31 +20486,31 @@
         <v>82</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>289</v>
+        <v>119</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>82</v>
@@ -20606,7 +20519,7 @@
         <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
@@ -20615,12 +20528,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>670</v>
+        <v>689</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20631,10 +20544,10 @@
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>82</v>
@@ -20643,19 +20556,19 @@
         <v>93</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20704,13 +20617,13 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>82</v>
@@ -20725,7 +20638,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20736,10 +20649,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>671</v>
+        <v>690</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20759,23 +20672,19 @@
         <v>82</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>82</v>
       </c>
@@ -20823,7 +20732,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20835,7 +20744,7 @@
         <v>82</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>82</v>
@@ -20844,7 +20753,7 @@
         <v>82</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>82</v>
@@ -20853,50 +20762,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C153" t="s" s="2">
-        <v>674</v>
-      </c>
+        <v>691</v>
+      </c>
+      <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>675</v>
+        <v>112</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>583</v>
+        <v>113</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>584</v>
+        <v>114</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>82</v>
       </c>
@@ -20932,64 +20837,62 @@
         <v>82</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>570</v>
+        <v>119</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO153" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>677</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>92</v>
@@ -21004,19 +20907,19 @@
         <v>93</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>678</v>
+        <v>133</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>583</v>
+        <v>262</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>584</v>
+        <v>263</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>574</v>
+        <v>264</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>575</v>
+        <v>265</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21065,7 +20968,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>570</v>
+        <v>267</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21074,7 +20977,7 @@
         <v>92</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>104</v>
@@ -21083,24 +20986,24 @@
         <v>82</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>578</v>
+        <v>268</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21114,29 +21017,27 @@
         <v>92</v>
       </c>
       <c r="H155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J155" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I155" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K155" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>680</v>
+        <v>271</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>681</v>
+        <v>272</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>683</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>82</v>
       </c>
@@ -21160,13 +21061,13 @@
         <v>82</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>685</v>
+        <v>82</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>82</v>
@@ -21184,7 +21085,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>679</v>
+        <v>274</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21193,7 +21094,7 @@
         <v>92</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>686</v>
+        <v>82</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>104</v>
@@ -21205,7 +21106,7 @@
         <v>82</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>82</v>
@@ -21216,21 +21117,21 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>93</v>
@@ -21239,22 +21140,20 @@
         <v>82</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>689</v>
+        <v>278</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>691</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>692</v>
+        <v>280</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>82</v>
@@ -21279,13 +21178,13 @@
         <v>82</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>693</v>
+        <v>82</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>694</v>
+        <v>82</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -21303,13 +21202,13 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>687</v>
+        <v>282</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>82</v>
@@ -21321,24 +21220,24 @@
         <v>82</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>695</v>
+        <v>82</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>696</v>
+        <v>283</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>697</v>
+        <v>82</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21349,7 +21248,7 @@
         <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>93</v>
@@ -21358,22 +21257,20 @@
         <v>82</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>699</v>
+        <v>106</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>700</v>
+        <v>286</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>702</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>703</v>
+        <v>288</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21422,13 +21319,13 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>698</v>
+        <v>289</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>82</v>
@@ -21443,7 +21340,7 @@
         <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>704</v>
+        <v>290</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>82</v>
@@ -21454,10 +21351,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21468,7 +21365,7 @@
         <v>80</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>82</v>
@@ -21477,21 +21374,23 @@
         <v>82</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>706</v>
+        <v>294</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>707</v>
+        <v>295</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
       </c>
@@ -21515,13 +21414,13 @@
         <v>82</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>709</v>
+        <v>82</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>710</v>
+        <v>82</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>82</v>
@@ -21539,7 +21438,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>705</v>
+        <v>298</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21557,24 +21456,24 @@
         <v>82</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>711</v>
+        <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>712</v>
+        <v>299</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>713</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21588,28 +21487,28 @@
         <v>92</v>
       </c>
       <c r="H159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J159" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K159" t="s" s="2">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>715</v>
+        <v>302</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>716</v>
+        <v>303</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>717</v>
+        <v>304</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>718</v>
+        <v>305</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
@@ -21634,13 +21533,13 @@
         <v>82</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>719</v>
+        <v>82</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>720</v>
+        <v>82</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -21658,7 +21557,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>714</v>
+        <v>306</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21679,7 +21578,7 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>721</v>
+        <v>307</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
@@ -21688,12 +21587,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>722</v>
+        <v>698</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>722</v>
+        <v>698</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21707,7 +21606,7 @@
         <v>92</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>82</v>
@@ -21716,15 +21615,17 @@
         <v>82</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>106</v>
+        <v>699</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>107</v>
+        <v>700</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N160" s="2"/>
+        <v>701</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>702</v>
+      </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>82</v>
@@ -21773,7 +21674,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>109</v>
+        <v>698</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21785,41 +21686,41 @@
         <v>82</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>82</v>
+        <v>703</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>82</v>
+        <v>704</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>82</v>
+        <v>705</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>82</v>
@@ -21831,17 +21732,15 @@
         <v>82</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>82</v>
@@ -21878,31 +21777,31 @@
         <v>82</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>82</v>
@@ -21920,16 +21819,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21939,29 +21838,27 @@
         <v>81</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>248</v>
+        <v>114</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>82</v>
       </c>
@@ -21997,19 +21894,19 @@
         <v>82</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22021,7 +21918,7 @@
         <v>82</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>82</v>
@@ -22030,7 +21927,7 @@
         <v>82</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>82</v>
@@ -22039,12 +21936,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22058,24 +21955,26 @@
         <v>92</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K163" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>107</v>
+        <v>449</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N163" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22124,7 +22023,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>109</v>
+        <v>452</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22133,10 +22032,10 @@
         <v>92</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>82</v>
@@ -22156,21 +22055,21 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>82</v>
@@ -22179,19 +22078,19 @@
         <v>82</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>113</v>
+        <v>455</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>114</v>
+        <v>456</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>115</v>
+        <v>457</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22217,43 +22116,43 @@
         <v>82</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>119</v>
+        <v>460</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>82</v>
@@ -22273,10 +22172,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22284,7 +22183,7 @@
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
         <v>92</v>
@@ -22299,20 +22198,18 @@
         <v>93</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>263</v>
+        <v>463</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>82</v>
       </c>
@@ -22360,7 +22257,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>267</v>
+        <v>465</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22381,7 +22278,7 @@
         <v>82</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>268</v>
+        <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>82</v>
@@ -22392,10 +22289,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22421,13 +22318,13 @@
         <v>106</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>271</v>
+        <v>467</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>272</v>
+        <v>468</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>273</v>
+        <v>469</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22477,7 +22374,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>274</v>
+        <v>470</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22498,7 +22395,7 @@
         <v>82</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>82</v>
@@ -22509,10 +22406,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22520,7 +22417,7 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
         <v>92</v>
@@ -22532,21 +22429,21 @@
         <v>82</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>167</v>
+        <v>713</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>278</v>
+        <v>714</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N167" s="2"/>
-      <c r="O167" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>82</v>
       </c>
@@ -22594,7 +22491,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>282</v>
+        <v>712</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22612,24 +22509,24 @@
         <v>82</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>82</v>
+        <v>717</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>283</v>
+        <v>718</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>82</v>
+        <v>719</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22643,27 +22540,25 @@
         <v>92</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>286</v>
+        <v>107</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="N168" s="2"/>
-      <c r="O168" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>82</v>
       </c>
@@ -22711,7 +22606,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>289</v>
+        <v>109</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22723,7 +22618,7 @@
         <v>82</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>82</v>
@@ -22732,7 +22627,7 @@
         <v>82</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>82</v>
@@ -22743,21 +22638,21 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>82</v>
@@ -22766,23 +22661,21 @@
         <v>82</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>293</v>
+        <v>112</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>295</v>
+        <v>114</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>82</v>
       </c>
@@ -22818,31 +22711,31 @@
         <v>82</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>298</v>
+        <v>119</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>82</v>
@@ -22851,7 +22744,7 @@
         <v>82</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>82</v>
@@ -22860,12 +22753,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22879,7 +22772,7 @@
         <v>92</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>82</v>
@@ -22891,17 +22784,15 @@
         <v>106</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>302</v>
+        <v>449</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>303</v>
+        <v>450</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>82</v>
       </c>
@@ -22949,7 +22840,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>306</v>
+        <v>452</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22958,7 +22849,7 @@
         <v>92</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>104</v>
@@ -22970,7 +22861,7 @@
         <v>82</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>82</v>
@@ -22979,12 +22870,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22998,25 +22889,25 @@
         <v>92</v>
       </c>
       <c r="H171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J171" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J171" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K171" t="s" s="2">
-        <v>734</v>
+        <v>133</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>735</v>
+        <v>455</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>736</v>
+        <v>456</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>737</v>
+        <v>457</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -23042,13 +22933,13 @@
         <v>82</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -23066,7 +22957,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>733</v>
+        <v>460</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23084,24 +22975,24 @@
         <v>82</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>738</v>
+        <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>739</v>
+        <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>740</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23115,24 +23006,26 @@
         <v>92</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>106</v>
+        <v>203</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N172" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23181,7 +23074,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>109</v>
+        <v>465</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23193,7 +23086,7 @@
         <v>82</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>82</v>
@@ -23213,21 +23106,21 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>742</v>
+        <v>725</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>82</v>
@@ -23236,19 +23129,19 @@
         <v>82</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>113</v>
+        <v>467</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>114</v>
+        <v>468</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>115</v>
+        <v>469</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23286,31 +23179,31 @@
         <v>82</v>
       </c>
       <c r="AB173" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC173" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE173" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>119</v>
+        <v>470</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>82</v>
@@ -23330,10 +23223,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23344,7 +23237,7 @@
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>93</v>
@@ -23353,21 +23246,23 @@
         <v>82</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>106</v>
+        <v>727</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>449</v>
+        <v>728</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>450</v>
+        <v>729</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O174" s="2"/>
+        <v>730</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
       </c>
@@ -23415,19 +23310,19 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>452</v>
+        <v>726</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>104</v>
+        <v>732</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>82</v>
@@ -23436,7 +23331,7 @@
         <v>82</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>82</v>
+        <v>733</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>82</v>
@@ -23447,10 +23342,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23470,20 +23365,18 @@
         <v>82</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>455</v>
+        <v>107</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23508,13 +23401,13 @@
         <v>82</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>82</v>
@@ -23532,7 +23425,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>460</v>
+        <v>109</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23544,7 +23437,7 @@
         <v>82</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>82</v>
@@ -23562,44 +23455,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>462</v>
+        <v>113</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>463</v>
+        <v>114</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>464</v>
+        <v>115</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -23649,19 +23542,19 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>465</v>
+        <v>119</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>82</v>
@@ -23681,44 +23574,46 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>82</v>
+        <v>737</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J177" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>467</v>
+        <v>738</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>468</v>
+        <v>739</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O177" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O177" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23766,19 +23661,19 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>470</v>
+        <v>741</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>82</v>
@@ -23798,10 +23693,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23824,17 +23719,15 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>751</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -23883,7 +23776,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23892,7 +23785,7 @@
         <v>92</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>82</v>
+        <v>746</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>104</v>
@@ -23901,24 +23794,24 @@
         <v>82</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>752</v>
+        <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>754</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23932,7 +23825,7 @@
         <v>92</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>82</v>
@@ -23941,13 +23834,13 @@
         <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>106</v>
+        <v>743</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>107</v>
+        <v>749</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>108</v>
+        <v>750</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23998,7 +23891,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>109</v>
+        <v>748</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24007,10 +23900,10 @@
         <v>92</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>82</v>
+        <v>746</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>82</v>
@@ -24019,7 +23912,7 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>82</v>
@@ -24030,21 +23923,21 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>82</v>
@@ -24056,18 +23949,20 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>112</v>
+        <v>232</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>113</v>
+        <v>752</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>114</v>
+        <v>753</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O180" s="2"/>
+        <v>754</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>755</v>
+      </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
       </c>
@@ -24091,52 +23986,52 @@
         <v>82</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>82</v>
+        <v>756</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>82</v>
+        <v>757</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>119</v>
+        <v>751</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>82</v>
+        <v>758</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>82</v>
+        <v>759</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>82</v>
@@ -24145,12 +24040,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24161,30 +24056,32 @@
         <v>80</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>449</v>
+        <v>761</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>450</v>
+        <v>762</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O181" s="2"/>
+        <v>763</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>764</v>
+      </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
       </c>
@@ -24208,13 +24105,13 @@
         <v>82</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>82</v>
+        <v>765</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>82</v>
+        <v>766</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>82</v>
@@ -24232,16 +24129,16 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>452</v>
+        <v>760</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>104</v>
@@ -24250,10 +24147,10 @@
         <v>82</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>82</v>
+        <v>758</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>82</v>
+        <v>759</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>82</v>
@@ -24264,10 +24161,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24287,21 +24184,21 @@
         <v>82</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>133</v>
+        <v>640</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>455</v>
+        <v>768</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O182" s="2"/>
+        <v>769</v>
+      </c>
+      <c r="N182" s="2"/>
+      <c r="O182" t="s" s="2">
+        <v>770</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
       </c>
@@ -24325,13 +24222,13 @@
         <v>82</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>82</v>
@@ -24349,7 +24246,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>460</v>
+        <v>767</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24379,12 +24276,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24398,26 +24295,24 @@
         <v>92</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>203</v>
+        <v>106</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>462</v>
+        <v>772</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24466,7 +24361,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>465</v>
+        <v>771</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24487,7 +24382,7 @@
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>82</v>
@@ -24498,10 +24393,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>760</v>
+        <v>774</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24512,7 +24407,7 @@
         <v>80</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>82</v>
@@ -24524,16 +24419,16 @@
         <v>93</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>106</v>
+        <v>775</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>467</v>
+        <v>776</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>468</v>
+        <v>777</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>469</v>
+        <v>778</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24583,13 +24478,13 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>470</v>
+        <v>774</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>82</v>
@@ -24604,7 +24499,7 @@
         <v>82</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>82</v>
+        <v>779</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>82</v>
@@ -24613,12 +24508,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24632,29 +24527,27 @@
         <v>81</v>
       </c>
       <c r="H185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J185" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K185" t="s" s="2">
-        <v>762</v>
+        <v>781</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>764</v>
+        <v>783</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>766</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>82</v>
       </c>
@@ -24702,7 +24595,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24714,7 +24607,7 @@
         <v>82</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>767</v>
+        <v>104</v>
       </c>
       <c r="AK185" t="s" s="2">
         <v>82</v>
@@ -24723,7 +24616,7 @@
         <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>82</v>
@@ -24734,10 +24627,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24748,7 +24641,7 @@
         <v>80</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>82</v>
@@ -24757,19 +24650,23 @@
         <v>82</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>106</v>
+        <v>727</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>107</v>
+        <v>786</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" s="2"/>
+        <v>787</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>789</v>
+      </c>
       <c r="P186" t="s" s="2">
         <v>82</v>
       </c>
@@ -24817,19 +24714,19 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>109</v>
+        <v>785</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>82</v>
@@ -24838,7 +24735,7 @@
         <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>82</v>
+        <v>790</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>82</v>
@@ -24849,21 +24746,21 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>82</v>
@@ -24875,17 +24772,15 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -24934,19 +24829,19 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>82</v>
@@ -24966,14 +24861,14 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>771</v>
+        <v>792</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>772</v>
+        <v>111</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -24986,26 +24881,24 @@
         <v>82</v>
       </c>
       <c r="I188" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>773</v>
+        <v>113</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>774</v>
+        <v>114</v>
       </c>
       <c r="N188" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O188" t="s" s="2">
-        <v>775</v>
-      </c>
+      <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>82</v>
       </c>
@@ -25053,7 +24946,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>776</v>
+        <v>119</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25083,44 +24976,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>82</v>
+        <v>737</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H189" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I189" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I189" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J189" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>778</v>
+        <v>112</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>779</v>
+        <v>738</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
       </c>
@@ -25168,19 +25065,19 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>777</v>
+        <v>741</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>781</v>
+        <v>82</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>82</v>
@@ -25189,7 +25086,7 @@
         <v>82</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>782</v>
+        <v>82</v>
       </c>
       <c r="AN189" t="s" s="2">
         <v>82</v>
@@ -25198,12 +25095,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25211,31 +25108,35 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G190" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J190" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K190" t="s" s="2">
-        <v>778</v>
+        <v>232</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="N190" s="2"/>
-      <c r="O190" s="2"/>
+        <v>796</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
       </c>
@@ -25259,13 +25160,13 @@
         <v>82</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>82</v>
@@ -25283,16 +25184,16 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>781</v>
+        <v>82</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>104</v>
@@ -25301,13 +25202,13 @@
         <v>82</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>82</v>
+        <v>798</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>782</v>
+        <v>411</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>82</v>
@@ -25315,10 +25216,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25338,22 +25239,22 @@
         <v>82</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>232</v>
+        <v>800</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>787</v>
+        <v>801</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>788</v>
+        <v>546</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>789</v>
+        <v>802</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>790</v>
+        <v>535</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -25378,13 +25279,13 @@
         <v>82</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>791</v>
+        <v>82</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>792</v>
+        <v>82</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>82</v>
@@ -25402,7 +25303,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -25420,24 +25321,24 @@
         <v>82</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>794</v>
+        <v>540</v>
       </c>
       <c r="AN191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25448,7 +25349,7 @@
         <v>80</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>82</v>
@@ -25463,16 +25364,16 @@
         <v>232</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>799</v>
+        <v>648</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -25497,13 +25398,13 @@
         <v>82</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>800</v>
+        <v>649</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>801</v>
+        <v>650</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
@@ -25521,16 +25422,16 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>104</v>
@@ -25539,10 +25440,10 @@
         <v>82</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>793</v>
+        <v>82</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>794</v>
+        <v>229</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>82</v>
@@ -25553,21 +25454,21 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>82</v>
+        <v>653</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>82</v>
@@ -25579,17 +25480,19 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>675</v>
+        <v>232</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="N193" s="2"/>
+        <v>810</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="O193" t="s" s="2">
-        <v>805</v>
+        <v>657</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>82</v>
@@ -25614,13 +25517,13 @@
         <v>82</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>82</v>
+        <v>811</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>82</v>
+        <v>812</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25638,13 +25541,13 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>82</v>
@@ -25656,24 +25559,24 @@
         <v>82</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25684,7 +25587,7 @@
         <v>80</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>82</v>
@@ -25696,16 +25599,20 @@
         <v>82</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>815</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
       </c>
@@ -25753,13 +25660,13 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>82</v>
@@ -25774,1316 +25681,17 @@
         <v>82</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>782</v>
+        <v>733</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="195" hidden="true">
-      <c r="A195" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="O195" s="2"/>
-      <c r="P195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO195" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="196" hidden="true">
-      <c r="A196" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="O196" s="2"/>
-      <c r="P196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO196" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="197" hidden="true">
-      <c r="A197" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="C197" s="2"/>
-      <c r="D197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E197" s="2"/>
-      <c r="F197" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J197" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K197" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="L197" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="P197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q197" s="2"/>
-      <c r="R197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF197" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="AG197" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ197" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM197" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="AN197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO197" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="198" hidden="true">
-      <c r="A198" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="C198" s="2"/>
-      <c r="D198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E198" s="2"/>
-      <c r="F198" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G198" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K198" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L198" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" s="2"/>
-      <c r="P198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q198" s="2"/>
-      <c r="R198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF198" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG198" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH198" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN198" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO198" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="199" hidden="true">
-      <c r="A199" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="C199" s="2"/>
-      <c r="D199" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E199" s="2"/>
-      <c r="F199" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K199" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L199" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O199" s="2"/>
-      <c r="P199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q199" s="2"/>
-      <c r="R199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF199" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG199" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ199" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO199" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="200" hidden="true">
-      <c r="A200" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="C200" s="2"/>
-      <c r="D200" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="E200" s="2"/>
-      <c r="F200" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I200" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J200" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K200" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L200" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="P200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q200" s="2"/>
-      <c r="R200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF200" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="AG200" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ200" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO200" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="201" hidden="true">
-      <c r="A201" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="C201" s="2"/>
-      <c r="D201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E201" s="2"/>
-      <c r="F201" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="G201" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J201" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K201" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L201" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="P201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q201" s="2"/>
-      <c r="R201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X201" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y201" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Z201" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF201" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="AG201" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH201" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ201" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL201" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="AM201" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AN201" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AO201" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="202" hidden="true">
-      <c r="A202" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="C202" s="2"/>
-      <c r="D202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E202" s="2"/>
-      <c r="F202" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G202" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J202" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K202" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="L202" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="P202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q202" s="2"/>
-      <c r="R202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF202" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="AG202" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH202" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ202" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL202" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="AM202" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AN202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO202" t="s" s="2">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="203" hidden="true">
-      <c r="A203" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="C203" s="2"/>
-      <c r="D203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E203" s="2"/>
-      <c r="F203" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G203" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K203" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L203" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="P203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q203" s="2"/>
-      <c r="R203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X203" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y203" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="Z203" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="AA203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF203" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="AG203" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH203" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI203" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AJ203" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM203" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AN203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO203" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="204" hidden="true">
-      <c r="A204" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="C204" s="2"/>
-      <c r="D204" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="E204" s="2"/>
-      <c r="F204" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G204" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K204" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="L204" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="M204" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="P204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q204" s="2"/>
-      <c r="R204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X204" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y204" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="Z204" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="AA204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF204" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="AG204" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH204" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ204" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL204" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="AM204" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AN204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO204" t="s" s="2">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="205" hidden="true">
-      <c r="A205" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="C205" s="2"/>
-      <c r="D205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E205" s="2"/>
-      <c r="F205" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G205" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K205" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L205" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="P205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q205" s="2"/>
-      <c r="R205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF205" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="AG205" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH205" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ205" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM205" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="AN205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO205" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO205">
+  <autoFilter ref="A1:AO194">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27093,7 +25701,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI204">
+  <conditionalFormatting sqref="A2:AI193">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
